--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488024_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488024_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C. PALOMARES CALDERON</t>
+          <t>M. GAMEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1729</v>
+        <v>4.5492</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0274</v>
+        <v>4.2558</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1455</v>
+        <v>0.2934</v>
       </c>
       <c r="G2" t="n">
-        <v>3.8667</v>
+        <v>3.4433</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9071</v>
+        <v>0.5581</v>
       </c>
       <c r="I2" t="n">
-        <v>2.9597</v>
+        <v>2.8853</v>
       </c>
       <c r="J2" t="n">
-        <v>4.7708</v>
+        <v>5.0173</v>
       </c>
       <c r="K2" t="n">
-        <v>2.6375</v>
+        <v>2.0247</v>
       </c>
       <c r="L2" t="n">
-        <v>2.1333</v>
+        <v>2.9926</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.9041</v>
+        <v>-1.5739</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.7304</v>
+        <v>-1.4666</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8264</v>
+        <v>-0.1073</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.3964</v>
+        <v>1.1893</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.9733</v>
+        <v>-0.9911</v>
       </c>
       <c r="R2" t="n">
-        <v>2.5769</v>
+        <v>2.1805</v>
       </c>
       <c r="S2" t="n">
-        <v>3.9098</v>
+        <v>-0.0835</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0229</v>
+        <v>0.2296</v>
       </c>
       <c r="U2" t="n">
-        <v>1.8868</v>
+        <v>-0.3131</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.4142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. GAMEZ SANCHEZ</t>
+          <t>C. PALOMARES CALDERON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6624</v>
+        <v>4.261</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3971</v>
+        <v>3.9298</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2653</v>
+        <v>0.3312</v>
       </c>
       <c r="G3" t="n">
-        <v>3.4433</v>
+        <v>3.8667</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5581</v>
+        <v>0.9071</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8853</v>
+        <v>2.9597</v>
       </c>
       <c r="J3" t="n">
-        <v>5.0173</v>
+        <v>4.7708</v>
       </c>
       <c r="K3" t="n">
-        <v>2.0247</v>
+        <v>2.6375</v>
       </c>
       <c r="L3" t="n">
-        <v>2.9926</v>
+        <v>2.1333</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.5739</v>
+        <v>-0.9041</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.4666</v>
+        <v>-1.7304</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1073</v>
+        <v>0.8264</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1893</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9911</v>
+        <v>-2.9733</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1805</v>
+        <v>2.5769</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0298</v>
+        <v>1.9978</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3709</v>
+        <v>0.9253</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3412</v>
+        <v>1.0726</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2243</v>
+        <v>4.056</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7769</v>
+        <v>2.5524</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4474</v>
+        <v>1.5036</v>
       </c>
       <c r="G4" t="n">
         <v>2.1275</v>
@@ -766,13 +766,13 @@
         <v>2.1805</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.7576</v>
+        <v>-0.926</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1232</v>
+        <v>-0.3477</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6345</v>
+        <v>-0.5783</v>
       </c>
       <c r="V4" t="n">
         <v>0.674</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. MALAVE FERNANDEZ</t>
+          <t>S. CURBELO MENENDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4129</v>
+        <v>2.0839</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2183</v>
+        <v>1.3156</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1947</v>
+        <v>0.7682</v>
       </c>
       <c r="G5" t="n">
-        <v>0.536</v>
+        <v>-0.4472</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0404</v>
+        <v>-2.6782</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4956</v>
+        <v>2.231</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5303</v>
+        <v>1.8055</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0404</v>
+        <v>-0.5442</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4899</v>
+        <v>2.3498</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0057</v>
+        <v>-2.2527</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-2.134</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0057</v>
+        <v>-0.1187</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3964</v>
+        <v>1.5858</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3964</v>
+        <v>2.5769</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1934</v>
+        <v>0.9453</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.312</v>
+        <v>0.5012</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1186</v>
+        <v>0.444</v>
       </c>
       <c r="V5" t="n">
-        <v>0.674</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.674</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. VICENTE BOSCH</t>
+          <t>D. MALAVE FERNANDEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1907</v>
+        <v>1.7633</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1243</v>
+        <v>0.4844</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0664</v>
+        <v>1.2789</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7754</v>
+        <v>0.536</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4159</v>
+        <v>0.0404</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3595</v>
+        <v>0.4956</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6908</v>
+        <v>0.5303</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1167</v>
+        <v>0.0404</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5742</v>
+        <v>0.4899</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.4662</v>
+        <v>0.0057</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.5326</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9337</v>
+        <v>0.0057</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7929</v>
+        <v>0.3964</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.784</v>
+        <v>0.3964</v>
       </c>
       <c r="S6" t="n">
-        <v>1.7768</v>
+        <v>0.1569</v>
       </c>
       <c r="T6" t="n">
-        <v>1.4355</v>
+        <v>-0.0459</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3413</v>
+        <v>0.2028</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6036</v>
+        <v>0.674</v>
       </c>
       <c r="W6" t="n">
-        <v>-1.0109</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.4074</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. SHERIFF</t>
+          <t>J. CERISUELO QUESADA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1242</v>
+        <v>1.266</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9789</v>
+        <v>1.417</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1453</v>
+        <v>-0.1509</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0472</v>
+        <v>-0.7477</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8391</v>
+        <v>-0.5123</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7919</v>
+        <v>-0.2354</v>
       </c>
       <c r="J7" t="n">
-        <v>0.248</v>
+        <v>1.1229</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1136</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3616</v>
+        <v>0.1607</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2952</v>
+        <v>-1.8705</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7255</v>
+        <v>-1.4745</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4303</v>
+        <v>-0.3961</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5947</v>
+        <v>0.1982</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5858</v>
+        <v>1.1893</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8433</v>
+        <v>0.201</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8518</v>
+        <v>0.0781</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0086</v>
+        <v>0.1229</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2666</v>
+        <v>1.6145</v>
       </c>
       <c r="W7" t="n">
-        <v>0.8701</v>
+        <v>1.2071</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1367</v>
+        <v>0.4074</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. CURBELO MENENDEZ</t>
+          <t>D. SHERIFF</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1232</v>
+        <v>1.1004</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5796</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5436</v>
+        <v>0.3419</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4472</v>
+        <v>-0.0472</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.6782</v>
+        <v>-0.8391</v>
       </c>
       <c r="I8" t="n">
-        <v>2.231</v>
+        <v>0.7919</v>
       </c>
       <c r="J8" t="n">
-        <v>1.8055</v>
+        <v>0.248</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5442</v>
+        <v>-0.1136</v>
       </c>
       <c r="L8" t="n">
-        <v>2.3498</v>
+        <v>0.3616</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.2527</v>
+        <v>-0.2952</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.134</v>
+        <v>-0.7255</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1187</v>
+        <v>0.4303</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5858</v>
+        <v>0.5947</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R8" t="n">
-        <v>2.5769</v>
+        <v>1.5858</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0154</v>
+        <v>0.8195</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2348</v>
+        <v>0.6316000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2194</v>
+        <v>0.188</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.8701</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.1367</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. CERISUELO QUESADA</t>
+          <t>J. VICENTE BOSCH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0166</v>
+        <v>0.54</v>
       </c>
       <c r="E9" t="n">
-        <v>1.1113</v>
+        <v>0.4736</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0948</v>
+        <v>0.0664</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7477</v>
+        <v>-0.7754</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5123</v>
+        <v>-0.4159</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2354</v>
+        <v>-0.3595</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1229</v>
+        <v>1.6908</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9622000000000001</v>
+        <v>1.1167</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1607</v>
+        <v>0.5742</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.8705</v>
+        <v>-2.4662</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4745</v>
+        <v>-1.5326</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3961</v>
+        <v>-0.9337</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1982</v>
+        <v>0.7929</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1893</v>
+        <v>1.784</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0485</v>
+        <v>1.1261</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2275</v>
+        <v>0.7848000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1791</v>
+        <v>0.3413</v>
       </c>
       <c r="V9" t="n">
-        <v>1.6145</v>
+        <v>-0.6036</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2071</v>
+        <v>-1.0109</v>
       </c>
       <c r="X9" t="n">
         <v>0.4074</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.09320000000000001</v>
+        <v>-0.2935</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6835</v>
+        <v>-1.8643</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7767</v>
+        <v>1.5708</v>
       </c>
       <c r="G10" t="n">
         <v>0.8733</v>
@@ -1234,13 +1234,13 @@
         <v>1.9822</v>
       </c>
       <c r="S10" t="n">
-        <v>1.8762</v>
+        <v>1.4894</v>
       </c>
       <c r="T10" t="n">
-        <v>1.1749</v>
+        <v>0.994</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7013</v>
+        <v>0.4954</v>
       </c>
       <c r="V10" t="n">
         <v>-0.674</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.0045</v>
+        <v>-0.3204</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0132</v>
+        <v>-0.4414</v>
       </c>
       <c r="F11" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.121</v>
       </c>
       <c r="G11" t="n">
         <v>-0.699</v>
@@ -1312,13 +1312,13 @@
         <v>0.3964</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4353</v>
+        <v>0.2487</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3744</v>
+        <v>0.1974</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0609</v>
+        <v>0.0514</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2666</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.7298</v>
+        <v>-1.5437</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.1757</v>
+        <v>-1.0738</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5541</v>
+        <v>-0.4699</v>
       </c>
       <c r="G12" t="n">
         <v>-0.5342</v>
@@ -1390,13 +1390,13 @@
         <v>0.5947</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7991</v>
+        <v>-0.613</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.312</v>
+        <v>-0.2101</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4871</v>
+        <v>-0.4029</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>17.2861</v>
+        <v>17.4622</v>
       </c>
       <c r="E13" t="n">
-        <v>11.3414</v>
+        <v>11.8077</v>
       </c>
       <c r="F13" t="n">
-        <v>5.9447</v>
+        <v>5.654599999999999</v>
       </c>
       <c r="G13" t="n">
         <v>7.5961</v>
@@ -1456,10 +1456,10 @@
         <v>-11.6514</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1596</v>
+        <v>0.1596000000000002</v>
       </c>
       <c r="P13" t="n">
-        <v>4.5592</v>
+        <v>4.559200000000001</v>
       </c>
       <c r="Q13" t="n">
         <v>-12.8844</v>
@@ -1468,16 +1468,16 @@
         <v>17.4436</v>
       </c>
       <c r="S13" t="n">
-        <v>5.1866</v>
+        <v>5.3622</v>
       </c>
       <c r="T13" t="n">
-        <v>3.2721</v>
+        <v>3.7383</v>
       </c>
       <c r="U13" t="n">
-        <v>1.9142</v>
+        <v>1.6241</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.05540000000000006</v>
+        <v>-0.05540000000000017</v>
       </c>
       <c r="W13" t="n">
         <v>1.866</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.8973</v>
+        <v>4.2355</v>
       </c>
       <c r="E14" t="n">
-        <v>4.653</v>
+        <v>4.5511</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.7557</v>
+        <v>-0.3156</v>
       </c>
       <c r="G14" t="n">
         <v>3.4977</v>
@@ -1546,13 +1546,13 @@
         <v>2.3787</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.8075</v>
+        <v>-1.4693</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6312</v>
+        <v>-0.7331</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.1763</v>
+        <v>-0.7362</v>
       </c>
       <c r="V14" t="n">
         <v>1.8107</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3706</v>
+        <v>1.1316</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2844</v>
+        <v>1.8769</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9137999999999999</v>
+        <v>-0.7453</v>
       </c>
       <c r="G15" t="n">
         <v>1.1224</v>
@@ -1624,13 +1624,13 @@
         <v>2.1805</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5337</v>
+        <v>-0.7727000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0034</v>
+        <v>-0.4109</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5303</v>
+        <v>-0.3618</v>
       </c>
       <c r="V15" t="n">
         <v>-0.4074</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0478</v>
+        <v>-0.0197</v>
       </c>
       <c r="E16" t="n">
         <v>-0.0576</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0098</v>
+        <v>0.0379</v>
       </c>
       <c r="G16" t="n">
         <v>1.3211</v>
@@ -1702,13 +1702,13 @@
         <v>0.3964</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7742</v>
+        <v>-0.7461</v>
       </c>
       <c r="T16" t="n">
         <v>-0.312</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4622</v>
+        <v>-0.4341</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.3272</v>
+        <v>-1.0111</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2006</v>
+        <v>0.0031</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1265</v>
+        <v>-1.0142</v>
       </c>
       <c r="G17" t="n">
         <v>-1.079</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2481</v>
+        <v>0.0679</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1872</v>
+        <v>0.0165</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0609</v>
+        <v>0.0514</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5521</v>
+        <v>-1.3483</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9932</v>
+        <v>-0.7894</v>
       </c>
       <c r="F18" t="n">
         <v>-0.5589</v>
@@ -1858,10 +1858,10 @@
         <v>0.1982</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4075</v>
+        <v>-0.2037</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3744</v>
+        <v>-0.1706</v>
       </c>
       <c r="U18" t="n">
         <v>-0.0331</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2189</v>
+        <v>-1.575</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.644</v>
+        <v>-0.4403</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5748</v>
+        <v>-1.1347</v>
       </c>
       <c r="G19" t="n">
         <v>-3.144</v>
@@ -1936,13 +1936,13 @@
         <v>0.3964</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.07489999999999999</v>
+        <v>0.569</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3158</v>
+        <v>0.5195</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3907</v>
+        <v>0.0495</v>
       </c>
       <c r="V19" t="n">
         <v>0.6036</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0607</v>
+        <v>-2.5474</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.7831</v>
+        <v>-1.7644</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2776</v>
+        <v>-0.7831</v>
       </c>
       <c r="G20" t="n">
         <v>-2.1583</v>
@@ -2014,13 +2014,13 @@
         <v>1.9822</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1888</v>
+        <v>-0.6755</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.6737</v>
+        <v>-0.655</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4849</v>
+        <v>-0.0205</v>
       </c>
       <c r="V20" t="n">
         <v>1.2775</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.1356</v>
+        <v>-3.7307</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.4883</v>
+        <v>-3.692</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6473</v>
+        <v>-0.0387</v>
       </c>
       <c r="G21" t="n">
         <v>-2.5924</v>
@@ -2092,13 +2092,13 @@
         <v>0.7929</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.671</v>
+        <v>-0.2661</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0072</v>
+        <v>-0.211</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6637999999999999</v>
+        <v>-0.0552</v>
       </c>
       <c r="V21" t="n">
         <v>-0.674</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.4781</v>
+        <v>-5.5372</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5817</v>
+        <v>-3.2948</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8963</v>
+        <v>-2.2424</v>
       </c>
       <c r="G22" t="n">
         <v>-1.981</v>
@@ -2170,13 +2170,13 @@
         <v>1.9822</v>
       </c>
       <c r="S22" t="n">
-        <v>1.7538</v>
+        <v>0.6946</v>
       </c>
       <c r="T22" t="n">
-        <v>0.9253</v>
+        <v>0.2122</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8285</v>
+        <v>0.4825</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2775</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.7221</v>
+        <v>-6.5138</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.1523</v>
+        <v>-3.356</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.5698</v>
+        <v>-3.1577</v>
       </c>
       <c r="G23" t="n">
         <v>-0.9056</v>
@@ -2248,13 +2248,13 @@
         <v>2.5769</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1692</v>
+        <v>-0.9609</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.253</v>
+        <v>-0.4568</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9161</v>
+        <v>-0.5041</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2775</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-18.2746</v>
+        <v>-16.9161</v>
       </c>
       <c r="E24" t="n">
         <v>-6.9634</v>
       </c>
       <c r="F24" t="n">
-        <v>-11.3109</v>
+        <v>-9.9527</v>
       </c>
       <c r="G24" t="n">
         <v>-7.261900000000001</v>
@@ -2326,13 +2326,13 @@
         <v>12.8844</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.1211</v>
+        <v>-3.7628</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.201</v>
+        <v>-2.2012</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.92</v>
+        <v>-1.5616</v>
       </c>
       <c r="V24" t="n">
         <v>0.05540000000000012</v>
